--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -1389,6 +1389,7 @@
     <row r="23">
       <c r="B23" s="9" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="B25" s="9" t="n"/>
     </row>
@@ -1416,12 +1417,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>1;4;1;false;0;0;0,0;0;0;0;0</t>
+          <t>1;4;1;false;0;0;0,0;1;0;0;0</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>1;-0.35;1;3;0;false;0;0;0,0;0;0;0;0</t>
+          <t>1;-0.35;1;3;0;false;0;0;0,0;1;0;0;0</t>
         </is>
       </c>
     </row>
